--- a/data/数据源7.6-7.10.xlsx
+++ b/data/数据源7.6-7.10.xlsx
@@ -4,13 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="优沃森需求明细&amp;岗位JD" sheetId="8" r:id="rId1"/>
     <sheet name="待入职表-优沃森" sheetId="10" r:id="rId2"/>
     <sheet name="面试记录表" sheetId="16" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'优沃森需求明细&amp;岗位JD'!$A$1:$Y$35</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -29,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="328">
   <si>
     <t>岗位</t>
   </si>
@@ -135,7 +138,7 @@
 5）执行力强，能跑、能谈、能跟、能落地，不适合只做管理协调、不愿意下场的人</t>
   </si>
   <si>
-    <t>中心仓</t>
+    <t>优沃森</t>
   </si>
   <si>
     <t>巢育敏</t>
@@ -160,9 +163,6 @@
   </si>
   <si>
     <t>面试中</t>
-  </si>
-  <si>
-    <t>周拓待定，1人待面试，2人待约面</t>
   </si>
   <si>
     <t>巢总</t>
@@ -191,9 +191,6 @@
 跨部门沟通协调能力强，能推动产品、运营、供应链等多部门协同，解决加盟商全周期问题；
 抗压性强，适应高频出差及高强度目标节奏，具备创业心态与开拓精神；
 熟练使用数据分析工具，能通过数据驱动团队管理与策略优化。</t>
-  </si>
-  <si>
-    <t>优沃森</t>
   </si>
   <si>
     <t>刘新风</t>
@@ -2225,7 +2222,8 @@
   <dimension ref="A1:Y35"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="19" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="16.5555555555556" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="11.2222222222222" customWidth="1"/>
     <col min="5" max="5" width="10.7777777777778" customWidth="1"/>
@@ -2382,28 +2380,26 @@
       <c r="U2" t="s">
         <v>35</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2"/>
+      <c r="W2" t="s">
         <v>36</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>37</v>
-      </c>
-      <c r="X2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="25.5" customHeight="1" spans="1:25">
       <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
         <v>39</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
         <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" t="s">
-        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>29</v>
@@ -2418,7 +2414,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -2445,48 +2441,48 @@
         <v>5</v>
       </c>
       <c r="T3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U3" t="s">
+        <v>43</v>
+      </c>
+      <c r="V3" t="s">
         <v>44</v>
       </c>
-      <c r="U3" t="s">
-        <v>45</v>
-      </c>
-      <c r="V3" t="s">
-        <v>46</v>
-      </c>
       <c r="W3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="25.5" customHeight="1" spans="1:25">
       <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
         <v>47</v>
-      </c>
-      <c r="B4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" t="s">
-        <v>49</v>
       </c>
       <c r="F4" t="s">
         <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -2513,57 +2509,57 @@
         <v>39</v>
       </c>
       <c r="T4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="W4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="25.5" customHeight="1" spans="1:25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="3">
         <v>4</v>
@@ -2579,57 +2575,57 @@
         <v>56</v>
       </c>
       <c r="T5" t="s">
+        <v>53</v>
+      </c>
+      <c r="U5" t="s">
+        <v>54</v>
+      </c>
+      <c r="V5" t="s">
         <v>55</v>
       </c>
-      <c r="U5" t="s">
-        <v>56</v>
-      </c>
-      <c r="V5" t="s">
-        <v>57</v>
-      </c>
       <c r="W5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="25.5" customHeight="1" spans="1:25">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F6" t="s">
         <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" s="3">
         <v>2</v>
@@ -2645,57 +2641,57 @@
         <v>56</v>
       </c>
       <c r="T6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="U6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="V6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="W6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="25.5" customHeight="1" spans="1:25">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F7" t="s">
         <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="3">
         <v>0</v>
@@ -2711,30 +2707,30 @@
         <v>56</v>
       </c>
       <c r="T7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="U7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="V7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="W7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="25.5" customHeight="1" spans="1:25">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
         <v>29</v>
@@ -2743,16 +2739,16 @@
         <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -2779,30 +2775,30 @@
         <v>31</v>
       </c>
       <c r="T8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="W8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="25.5" customHeight="1" spans="1:25">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
         <v>29</v>
@@ -2811,16 +2807,16 @@
         <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -2847,30 +2843,30 @@
         <v>31</v>
       </c>
       <c r="T9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="W9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="25.5" customHeight="1" spans="1:25">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
         <v>29</v>
@@ -2879,16 +2875,16 @@
         <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -2915,30 +2911,30 @@
         <v>31</v>
       </c>
       <c r="T10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="W10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" customFormat="1" ht="25.5" customHeight="1" spans="1:25">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
         <v>29</v>
@@ -2947,16 +2943,16 @@
         <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -2983,30 +2979,30 @@
         <v>24</v>
       </c>
       <c r="T11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="W11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" customFormat="1" ht="25.5" customHeight="1" spans="1:25">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E12" t="s">
         <v>29</v>
@@ -3015,16 +3011,16 @@
         <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -3051,24 +3047,24 @@
         <v>10</v>
       </c>
       <c r="T12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="W12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="25.5" customHeight="1" spans="1:25">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
@@ -3083,13 +3079,13 @@
         <v>30</v>
       </c>
       <c r="I13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -3116,48 +3112,48 @@
         <v>14</v>
       </c>
       <c r="T13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="W13" t="s">
+        <v>36</v>
+      </c>
+      <c r="X13" t="s">
         <v>37</v>
-      </c>
-      <c r="X13" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="25.5" customHeight="1" spans="1:25">
       <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
         <v>79</v>
       </c>
-      <c r="B14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>81</v>
-      </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s">
         <v>30</v>
       </c>
       <c r="I14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L14">
         <v>2</v>
@@ -3184,39 +3180,39 @@
         <v>14</v>
       </c>
       <c r="T14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="W14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" customFormat="1" ht="25.5" customHeight="1" spans="1:25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
         <v>30</v>
       </c>
       <c r="I15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J15">
         <v>4</v>
       </c>
       <c r="K15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3241,45 +3237,45 @@
         <v>57</v>
       </c>
       <c r="T15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="U15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="V15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" customFormat="1" ht="25.5" customHeight="1" spans="1:25">
       <c r="A16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
         <v>86</v>
       </c>
-      <c r="B16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" t="s">
-        <v>88</v>
-      </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
         <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L16">
         <v>2</v>
@@ -3306,42 +3302,42 @@
         <v>18</v>
       </c>
       <c r="T16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" t="s">
         <v>90</v>
       </c>
-      <c r="B17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="I17" t="s">
         <v>49</v>
       </c>
-      <c r="F17" t="s">
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
         <v>91</v>
-      </c>
-      <c r="G17" t="s">
-        <v>92</v>
-      </c>
-      <c r="I17" t="s">
-        <v>51</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17" t="s">
-        <v>93</v>
       </c>
       <c r="L17">
         <v>1</v>
@@ -3366,48 +3362,48 @@
         <v>36</v>
       </c>
       <c r="T17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="W17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F18" t="s">
         <v>30</v>
       </c>
       <c r="G18" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L18">
         <v>1</v>
@@ -3434,42 +3430,42 @@
         <v>18</v>
       </c>
       <c r="T18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" t="s">
+        <v>90</v>
+      </c>
+      <c r="I19" t="s">
         <v>49</v>
       </c>
-      <c r="F19" t="s">
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="s">
         <v>91</v>
-      </c>
-      <c r="G19" t="s">
-        <v>92</v>
-      </c>
-      <c r="I19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" t="s">
-        <v>93</v>
       </c>
       <c r="L19">
         <v>2</v>
@@ -3494,42 +3490,42 @@
         <v>36</v>
       </c>
       <c r="T19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="W19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
         <v>30</v>
       </c>
       <c r="I20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L20">
         <v>1</v>
@@ -3556,36 +3552,36 @@
         <v>4</v>
       </c>
       <c r="T20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F21" t="s">
         <v>30</v>
       </c>
       <c r="I21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J21">
         <v>4</v>
       </c>
       <c r="K21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3610,39 +3606,39 @@
         <v>57</v>
       </c>
       <c r="T21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="U21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="V21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s">
         <v>30</v>
       </c>
       <c r="I22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L22">
         <v>1</v>
@@ -3669,45 +3665,45 @@
         <v>5</v>
       </c>
       <c r="T22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" t="s">
         <v>107</v>
-      </c>
-      <c r="B23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" t="s">
-        <v>109</v>
       </c>
       <c r="F23" t="s">
         <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J23">
         <v>2</v>
       </c>
       <c r="K23" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L23">
         <v>3</v>
@@ -3732,27 +3728,27 @@
         <v>28</v>
       </c>
       <c r="T23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="V23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
         <v>29</v>
@@ -3761,16 +3757,16 @@
         <v>30</v>
       </c>
       <c r="G24" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L24">
         <v>1</v>
@@ -3797,30 +3793,30 @@
         <v>8</v>
       </c>
       <c r="T24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U24" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="V24" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
         <v>29</v>
@@ -3829,7 +3825,7 @@
         <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I25" t="s">
         <v>32</v>
@@ -3838,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L25">
         <v>1</v>
@@ -3863,7 +3859,7 @@
         <v>17</v>
       </c>
       <c r="T25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U25" t="s">
         <v>35</v>
@@ -3871,34 +3867,34 @@
     </row>
     <row r="26" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" t="s">
+        <v>89</v>
+      </c>
+      <c r="G26" t="s">
         <v>120</v>
       </c>
-      <c r="B26" t="s">
+      <c r="I26" t="s">
         <v>121</v>
       </c>
-      <c r="C26" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E26" t="s">
-        <v>49</v>
-      </c>
-      <c r="F26" t="s">
-        <v>91</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" t="s">
         <v>122</v>
-      </c>
-      <c r="I26" t="s">
-        <v>123</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26" t="s">
-        <v>124</v>
       </c>
       <c r="L26">
         <v>10</v>
@@ -3929,21 +3925,21 @@
         <v>35</v>
       </c>
       <c r="V26" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s">
         <v>29</v>
@@ -3952,10 +3948,10 @@
         <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I27" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3994,16 +3990,16 @@
     </row>
     <row r="28" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E28" t="s">
         <v>29</v>
@@ -4012,16 +4008,16 @@
         <v>30</v>
       </c>
       <c r="G28" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -4052,39 +4048,39 @@
         <v>35</v>
       </c>
       <c r="V28" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E29" t="s">
         <v>29</v>
       </c>
       <c r="F29" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I29" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J29">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L29">
         <v>6</v>
@@ -4115,18 +4111,21 @@
         <v>35</v>
       </c>
       <c r="V29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A30" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="C30" t="s">
+        <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E30" t="s">
         <v>29</v>
@@ -4135,16 +4134,16 @@
         <v>30</v>
       </c>
       <c r="G30" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I30" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J30">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L30">
         <v>1</v>
@@ -4171,27 +4170,30 @@
         <v>8</v>
       </c>
       <c r="T30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="V30" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="W30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A31" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>125</v>
+      </c>
+      <c r="C31" t="s">
+        <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E31" t="s">
         <v>29</v>
@@ -4200,16 +4202,16 @@
         <v>30</v>
       </c>
       <c r="G31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I31" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L31">
         <v>1</v>
@@ -4234,7 +4236,7 @@
         <v>17</v>
       </c>
       <c r="T31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U31" t="s">
         <v>35</v>
@@ -4242,13 +4244,16 @@
     </row>
     <row r="32" customFormat="1" ht="25.5" customHeight="1" spans="1:23">
       <c r="A32" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="C32" t="s">
+        <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E32" t="s">
         <v>29</v>
@@ -4257,16 +4262,16 @@
         <v>30</v>
       </c>
       <c r="G32" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I32" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L32">
         <v>1</v>
@@ -4293,21 +4298,24 @@
         <v>7</v>
       </c>
       <c r="T32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U32" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="V32" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="W32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" customFormat="1" ht="25.5" customHeight="1" spans="1:22">
       <c r="A33" t="s">
-        <v>145</v>
+        <v>143</v>
+      </c>
+      <c r="C33" t="s">
+        <v>27</v>
       </c>
       <c r="D33" t="s">
         <v>28</v>
@@ -4316,19 +4324,19 @@
         <v>29</v>
       </c>
       <c r="F33" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I33" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L33">
         <v>2</v>
@@ -4359,36 +4367,39 @@
         <v>35</v>
       </c>
       <c r="V33" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" customFormat="1" ht="25.5" customHeight="1" spans="1:22">
       <c r="A34" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" t="s">
         <v>147</v>
       </c>
-      <c r="B34" t="s">
-        <v>148</v>
-      </c>
-      <c r="D34" t="s">
-        <v>149</v>
-      </c>
       <c r="E34" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F34" t="s">
         <v>30</v>
       </c>
       <c r="G34" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J34">
         <v>3</v>
       </c>
       <c r="K34" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L34">
         <v>1</v>
@@ -4418,31 +4429,34 @@
     </row>
     <row r="35" customFormat="1" ht="25.5" customHeight="1" spans="1:22">
       <c r="A35" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>129</v>
+      </c>
+      <c r="C35" t="s">
+        <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F35" t="s">
         <v>30</v>
       </c>
       <c r="G35" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I35" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -4471,6 +4485,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Y35" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <dataValidations count="5">
     <dataValidation type="list" sqref="D2:D34">
       <formula1>"张蓉蓉,吴双双,巢育敏,刘新风,后台"</formula1>
@@ -4518,52 +4535,52 @@
   <sheetData>
     <row r="1" ht="13" customHeight="1" spans="1:16">
       <c r="A1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="2" ht="25.5" customHeight="1" spans="1:16">
@@ -4571,49 +4588,49 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F2" t="s">
         <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I2" s="2">
         <v>46156</v>
       </c>
       <c r="J2" t="s">
+        <v>169</v>
+      </c>
+      <c r="K2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" t="s">
+        <v>170</v>
+      </c>
+      <c r="N2" t="s">
         <v>171</v>
       </c>
-      <c r="K2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>172</v>
       </c>
-      <c r="N2" t="s">
-        <v>173</v>
-      </c>
-      <c r="O2" t="s">
-        <v>174</v>
-      </c>
       <c r="P2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" ht="25.5" customHeight="1" spans="1:16">
@@ -4621,49 +4638,49 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" t="s">
         <v>168</v>
       </c>
-      <c r="D3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" t="s">
-        <v>170</v>
-      </c>
       <c r="H3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I3" s="2">
         <v>46160</v>
       </c>
       <c r="J3" t="s">
+        <v>174</v>
+      </c>
+      <c r="K3" t="s">
+        <v>79</v>
+      </c>
+      <c r="L3" t="s">
+        <v>79</v>
+      </c>
+      <c r="M3" t="s">
+        <v>175</v>
+      </c>
+      <c r="N3" t="s">
         <v>176</v>
       </c>
-      <c r="K3" t="s">
-        <v>81</v>
-      </c>
-      <c r="L3" t="s">
-        <v>81</v>
-      </c>
-      <c r="M3" t="s">
-        <v>177</v>
-      </c>
-      <c r="N3" t="s">
-        <v>178</v>
-      </c>
       <c r="O3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:16">
@@ -4671,49 +4688,49 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F4" t="s">
         <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I4" s="2">
         <v>46167</v>
       </c>
       <c r="J4" t="s">
+        <v>174</v>
+      </c>
+      <c r="K4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" t="s">
+        <v>170</v>
+      </c>
+      <c r="N4" t="s">
         <v>176</v>
       </c>
-      <c r="K4" t="s">
-        <v>53</v>
-      </c>
-      <c r="L4" t="s">
-        <v>53</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="O4" t="s">
         <v>172</v>
       </c>
-      <c r="N4" t="s">
-        <v>178</v>
-      </c>
-      <c r="O4" t="s">
-        <v>174</v>
-      </c>
       <c r="P4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" ht="25.5" customHeight="1" spans="1:16">
@@ -4721,49 +4738,49 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" t="s">
         <v>168</v>
       </c>
-      <c r="D5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" t="s">
-        <v>170</v>
-      </c>
       <c r="H5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I5" s="2">
         <v>46168</v>
       </c>
       <c r="J5" t="s">
+        <v>174</v>
+      </c>
+      <c r="K5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L5" t="s">
+        <v>51</v>
+      </c>
+      <c r="M5" t="s">
+        <v>170</v>
+      </c>
+      <c r="N5" t="s">
         <v>176</v>
       </c>
-      <c r="K5" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" t="s">
-        <v>53</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="O5" t="s">
         <v>172</v>
       </c>
-      <c r="N5" t="s">
-        <v>178</v>
-      </c>
-      <c r="O5" t="s">
-        <v>174</v>
-      </c>
       <c r="P5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" ht="25.5" customHeight="1" spans="1:16">
@@ -4771,49 +4788,49 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
         <v>168</v>
       </c>
-      <c r="D6" t="s">
-        <v>182</v>
-      </c>
-      <c r="E6" t="s">
-        <v>169</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6" t="s">
-        <v>170</v>
-      </c>
       <c r="H6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I6" s="2">
         <v>46174</v>
       </c>
       <c r="J6" t="s">
+        <v>174</v>
+      </c>
+      <c r="K6" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M6" t="s">
+        <v>170</v>
+      </c>
+      <c r="N6" t="s">
         <v>176</v>
       </c>
-      <c r="K6" t="s">
-        <v>53</v>
-      </c>
-      <c r="L6" t="s">
-        <v>53</v>
-      </c>
-      <c r="M6" t="s">
+      <c r="O6" t="s">
         <v>172</v>
       </c>
-      <c r="N6" t="s">
-        <v>178</v>
-      </c>
-      <c r="O6" t="s">
-        <v>174</v>
-      </c>
       <c r="P6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" ht="25.5" customHeight="1" spans="1:16">
@@ -4821,31 +4838,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F7" t="s">
         <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I7" s="2">
         <v>46167</v>
       </c>
       <c r="J7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K7" t="s">
         <v>28</v>
@@ -4854,16 +4871,16 @@
         <v>28</v>
       </c>
       <c r="M7" t="s">
+        <v>170</v>
+      </c>
+      <c r="N7" t="s">
+        <v>176</v>
+      </c>
+      <c r="O7" t="s">
         <v>172</v>
       </c>
-      <c r="N7" t="s">
-        <v>178</v>
-      </c>
-      <c r="O7" t="s">
-        <v>174</v>
-      </c>
       <c r="P7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" ht="25.5" customHeight="1" spans="1:16">
@@ -4871,49 +4888,49 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" t="s">
         <v>168</v>
       </c>
-      <c r="D8" t="s">
-        <v>185</v>
-      </c>
-      <c r="E8" t="s">
-        <v>169</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" t="s">
-        <v>170</v>
-      </c>
       <c r="H8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I8" s="2">
         <v>46161</v>
       </c>
       <c r="J8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L8" t="s">
+        <v>79</v>
+      </c>
+      <c r="M8" t="s">
+        <v>175</v>
+      </c>
+      <c r="N8" t="s">
         <v>176</v>
       </c>
-      <c r="K8" t="s">
-        <v>81</v>
-      </c>
-      <c r="L8" t="s">
-        <v>81</v>
-      </c>
-      <c r="M8" t="s">
-        <v>177</v>
-      </c>
-      <c r="N8" t="s">
-        <v>178</v>
-      </c>
       <c r="O8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" ht="25.5" customHeight="1" spans="1:16">
@@ -4921,49 +4938,49 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
+        <v>166</v>
+      </c>
+      <c r="D9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" t="s">
         <v>168</v>
       </c>
-      <c r="D9" t="s">
-        <v>187</v>
-      </c>
-      <c r="E9" t="s">
-        <v>169</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" t="s">
-        <v>170</v>
-      </c>
       <c r="H9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I9" s="2">
         <v>46161</v>
       </c>
       <c r="J9" t="s">
+        <v>174</v>
+      </c>
+      <c r="K9" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" t="s">
+        <v>79</v>
+      </c>
+      <c r="M9" t="s">
+        <v>175</v>
+      </c>
+      <c r="N9" t="s">
         <v>176</v>
       </c>
-      <c r="K9" t="s">
-        <v>81</v>
-      </c>
-      <c r="L9" t="s">
-        <v>81</v>
-      </c>
-      <c r="M9" t="s">
-        <v>177</v>
-      </c>
-      <c r="N9" t="s">
-        <v>178</v>
-      </c>
       <c r="O9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" ht="25.5" customHeight="1" spans="1:16">
@@ -4971,49 +4988,49 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E10" t="s">
+        <v>167</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" t="s">
         <v>168</v>
       </c>
-      <c r="D10" t="s">
-        <v>188</v>
-      </c>
-      <c r="E10" t="s">
-        <v>169</v>
-      </c>
-      <c r="F10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" t="s">
-        <v>170</v>
-      </c>
       <c r="H10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I10" s="2">
         <v>46167</v>
       </c>
       <c r="J10" t="s">
+        <v>174</v>
+      </c>
+      <c r="K10" t="s">
+        <v>86</v>
+      </c>
+      <c r="L10" t="s">
+        <v>86</v>
+      </c>
+      <c r="M10" t="s">
+        <v>175</v>
+      </c>
+      <c r="N10" t="s">
         <v>176</v>
       </c>
-      <c r="K10" t="s">
-        <v>88</v>
-      </c>
-      <c r="L10" t="s">
-        <v>88</v>
-      </c>
-      <c r="M10" t="s">
-        <v>177</v>
-      </c>
-      <c r="N10" t="s">
-        <v>178</v>
-      </c>
       <c r="O10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" ht="25.5" customHeight="1" spans="1:16">
@@ -5021,49 +5038,49 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11" t="s">
+        <v>167</v>
+      </c>
+      <c r="F11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" t="s">
+        <v>168</v>
+      </c>
+      <c r="H11" t="s">
         <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>168</v>
-      </c>
-      <c r="D11" t="s">
-        <v>189</v>
-      </c>
-      <c r="E11" t="s">
-        <v>169</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" t="s">
-        <v>170</v>
-      </c>
-      <c r="H11" t="s">
-        <v>79</v>
       </c>
       <c r="I11" s="2">
         <v>46170</v>
       </c>
       <c r="J11" t="s">
+        <v>174</v>
+      </c>
+      <c r="K11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" t="s">
+        <v>79</v>
+      </c>
+      <c r="M11" t="s">
+        <v>175</v>
+      </c>
+      <c r="N11" t="s">
         <v>176</v>
       </c>
-      <c r="K11" t="s">
-        <v>81</v>
-      </c>
-      <c r="L11" t="s">
-        <v>81</v>
-      </c>
-      <c r="M11" t="s">
-        <v>177</v>
-      </c>
-      <c r="N11" t="s">
-        <v>178</v>
-      </c>
       <c r="O11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" ht="25.5" customHeight="1" spans="1:16">
@@ -5071,49 +5088,49 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
+        <v>166</v>
+      </c>
+      <c r="D12" t="s">
+        <v>188</v>
+      </c>
+      <c r="E12" t="s">
+        <v>167</v>
+      </c>
+      <c r="F12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" t="s">
         <v>168</v>
       </c>
-      <c r="D12" t="s">
-        <v>190</v>
-      </c>
-      <c r="E12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" t="s">
-        <v>170</v>
-      </c>
       <c r="H12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I12" s="2">
         <v>46164</v>
       </c>
       <c r="J12" t="s">
+        <v>174</v>
+      </c>
+      <c r="K12" t="s">
+        <v>86</v>
+      </c>
+      <c r="L12" t="s">
+        <v>86</v>
+      </c>
+      <c r="M12" t="s">
+        <v>175</v>
+      </c>
+      <c r="N12" t="s">
         <v>176</v>
       </c>
-      <c r="K12" t="s">
-        <v>88</v>
-      </c>
-      <c r="L12" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" t="s">
-        <v>177</v>
-      </c>
-      <c r="N12" t="s">
-        <v>178</v>
-      </c>
       <c r="O12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" ht="25.5" customHeight="1" spans="1:16">
@@ -5121,49 +5138,49 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
+        <v>166</v>
+      </c>
+      <c r="D13" t="s">
+        <v>190</v>
+      </c>
+      <c r="E13" t="s">
+        <v>167</v>
+      </c>
+      <c r="F13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" t="s">
         <v>168</v>
       </c>
-      <c r="D13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E13" t="s">
-        <v>169</v>
-      </c>
-      <c r="F13" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" t="s">
-        <v>170</v>
-      </c>
       <c r="H13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I13" s="2">
         <v>46181</v>
       </c>
       <c r="J13" t="s">
+        <v>174</v>
+      </c>
+      <c r="K13" t="s">
+        <v>51</v>
+      </c>
+      <c r="L13" t="s">
+        <v>51</v>
+      </c>
+      <c r="M13" t="s">
+        <v>170</v>
+      </c>
+      <c r="N13" t="s">
         <v>176</v>
       </c>
-      <c r="K13" t="s">
-        <v>53</v>
-      </c>
-      <c r="L13" t="s">
-        <v>53</v>
-      </c>
-      <c r="M13" t="s">
+      <c r="O13" t="s">
         <v>172</v>
       </c>
-      <c r="N13" t="s">
-        <v>178</v>
-      </c>
-      <c r="O13" t="s">
-        <v>174</v>
-      </c>
       <c r="P13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" ht="25.5" customHeight="1" spans="1:16">
@@ -5171,49 +5188,49 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
+        <v>166</v>
+      </c>
+      <c r="D14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E14" t="s">
+        <v>167</v>
+      </c>
+      <c r="F14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" t="s">
         <v>168</v>
       </c>
-      <c r="D14" t="s">
-        <v>193</v>
-      </c>
-      <c r="E14" t="s">
-        <v>169</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14" t="s">
-        <v>170</v>
-      </c>
       <c r="H14" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I14" s="2">
         <v>46174</v>
       </c>
       <c r="J14" t="s">
+        <v>174</v>
+      </c>
+      <c r="K14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L14" t="s">
+        <v>86</v>
+      </c>
+      <c r="M14" t="s">
+        <v>175</v>
+      </c>
+      <c r="N14" t="s">
         <v>176</v>
       </c>
-      <c r="K14" t="s">
-        <v>88</v>
-      </c>
-      <c r="L14" t="s">
-        <v>88</v>
-      </c>
-      <c r="M14" t="s">
-        <v>177</v>
-      </c>
-      <c r="N14" t="s">
-        <v>178</v>
-      </c>
       <c r="O14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" ht="25.5" customHeight="1" spans="1:16">
@@ -5221,49 +5238,49 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" t="s">
+        <v>167</v>
+      </c>
+      <c r="F15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" t="s">
         <v>168</v>
       </c>
-      <c r="D15" t="s">
-        <v>195</v>
-      </c>
-      <c r="E15" t="s">
-        <v>169</v>
-      </c>
-      <c r="F15" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" t="s">
-        <v>170</v>
-      </c>
       <c r="H15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I15" s="2">
         <v>46174</v>
       </c>
       <c r="J15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K15" t="s">
+        <v>86</v>
+      </c>
+      <c r="L15" t="s">
+        <v>86</v>
+      </c>
+      <c r="M15" t="s">
+        <v>175</v>
+      </c>
+      <c r="N15" t="s">
         <v>176</v>
       </c>
-      <c r="K15" t="s">
-        <v>88</v>
-      </c>
-      <c r="L15" t="s">
-        <v>88</v>
-      </c>
-      <c r="M15" t="s">
-        <v>177</v>
-      </c>
-      <c r="N15" t="s">
-        <v>178</v>
-      </c>
       <c r="O15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" ht="25.5" customHeight="1" spans="1:16">
@@ -5271,49 +5288,49 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F16" t="s">
         <v>29</v>
       </c>
       <c r="G16" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H16" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I16" s="2">
         <v>46181</v>
       </c>
       <c r="J16" t="s">
+        <v>174</v>
+      </c>
+      <c r="K16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M16" t="s">
+        <v>170</v>
+      </c>
+      <c r="N16" t="s">
         <v>176</v>
       </c>
-      <c r="K16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L16" t="s">
-        <v>53</v>
-      </c>
-      <c r="M16" t="s">
+      <c r="O16" t="s">
         <v>172</v>
       </c>
-      <c r="N16" t="s">
-        <v>178</v>
-      </c>
-      <c r="O16" t="s">
-        <v>174</v>
-      </c>
       <c r="P16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" ht="25.5" customHeight="1" spans="1:16">
@@ -5321,49 +5338,49 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D17" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F17" t="s">
         <v>29</v>
       </c>
       <c r="G17" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H17" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I17" s="2">
         <v>46188</v>
       </c>
       <c r="J17" t="s">
+        <v>174</v>
+      </c>
+      <c r="K17" t="s">
+        <v>51</v>
+      </c>
+      <c r="L17" t="s">
+        <v>51</v>
+      </c>
+      <c r="M17" t="s">
+        <v>170</v>
+      </c>
+      <c r="N17" t="s">
         <v>176</v>
       </c>
-      <c r="K17" t="s">
-        <v>53</v>
-      </c>
-      <c r="L17" t="s">
-        <v>53</v>
-      </c>
-      <c r="M17" t="s">
+      <c r="O17" t="s">
         <v>172</v>
       </c>
-      <c r="N17" t="s">
-        <v>178</v>
-      </c>
-      <c r="O17" t="s">
-        <v>174</v>
-      </c>
       <c r="P17" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" ht="25.5" customHeight="1" spans="1:16">
@@ -5371,49 +5388,49 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D18" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E18" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F18" t="s">
         <v>29</v>
       </c>
       <c r="G18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H18" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I18" s="2">
         <v>46188</v>
       </c>
       <c r="J18" t="s">
+        <v>174</v>
+      </c>
+      <c r="K18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L18" t="s">
+        <v>51</v>
+      </c>
+      <c r="M18" t="s">
+        <v>170</v>
+      </c>
+      <c r="N18" t="s">
         <v>176</v>
       </c>
-      <c r="K18" t="s">
-        <v>53</v>
-      </c>
-      <c r="L18" t="s">
-        <v>53</v>
-      </c>
-      <c r="M18" t="s">
+      <c r="O18" t="s">
         <v>172</v>
       </c>
-      <c r="N18" t="s">
-        <v>178</v>
-      </c>
-      <c r="O18" t="s">
-        <v>174</v>
-      </c>
       <c r="P18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" ht="25.5" customHeight="1" spans="1:16">
@@ -5421,49 +5438,49 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" t="s">
+        <v>197</v>
+      </c>
+      <c r="E19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" t="s">
         <v>168</v>
       </c>
-      <c r="D19" t="s">
-        <v>199</v>
-      </c>
-      <c r="E19" t="s">
-        <v>169</v>
-      </c>
-      <c r="F19" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19" t="s">
-        <v>170</v>
-      </c>
       <c r="H19" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I19" s="2">
         <v>46188</v>
       </c>
       <c r="J19" t="s">
+        <v>174</v>
+      </c>
+      <c r="K19" t="s">
+        <v>51</v>
+      </c>
+      <c r="L19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M19" t="s">
+        <v>170</v>
+      </c>
+      <c r="N19" t="s">
         <v>176</v>
       </c>
-      <c r="K19" t="s">
-        <v>53</v>
-      </c>
-      <c r="L19" t="s">
-        <v>53</v>
-      </c>
-      <c r="M19" t="s">
+      <c r="O19" t="s">
         <v>172</v>
       </c>
-      <c r="N19" t="s">
-        <v>178</v>
-      </c>
-      <c r="O19" t="s">
-        <v>174</v>
-      </c>
       <c r="P19" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" ht="25.5" customHeight="1" spans="1:16">
@@ -5471,49 +5488,49 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F20" t="s">
         <v>29</v>
       </c>
       <c r="G20" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H20" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I20" s="2">
         <v>46188</v>
       </c>
       <c r="J20" t="s">
+        <v>174</v>
+      </c>
+      <c r="K20" t="s">
+        <v>51</v>
+      </c>
+      <c r="L20" t="s">
+        <v>51</v>
+      </c>
+      <c r="M20" t="s">
+        <v>170</v>
+      </c>
+      <c r="N20" t="s">
         <v>176</v>
       </c>
-      <c r="K20" t="s">
-        <v>53</v>
-      </c>
-      <c r="L20" t="s">
-        <v>53</v>
-      </c>
-      <c r="M20" t="s">
+      <c r="O20" t="s">
         <v>172</v>
       </c>
-      <c r="N20" t="s">
-        <v>178</v>
-      </c>
-      <c r="O20" t="s">
-        <v>174</v>
-      </c>
       <c r="P20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" ht="25.5" customHeight="1" spans="1:16">
@@ -5521,49 +5538,49 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
+        <v>166</v>
+      </c>
+      <c r="D21" t="s">
+        <v>199</v>
+      </c>
+      <c r="E21" t="s">
+        <v>167</v>
+      </c>
+      <c r="F21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" t="s">
         <v>168</v>
       </c>
-      <c r="D21" t="s">
-        <v>201</v>
-      </c>
-      <c r="E21" t="s">
-        <v>169</v>
-      </c>
-      <c r="F21" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21" t="s">
-        <v>170</v>
-      </c>
       <c r="H21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I21" s="2">
         <v>46196</v>
       </c>
       <c r="J21" t="s">
+        <v>174</v>
+      </c>
+      <c r="K21" t="s">
+        <v>93</v>
+      </c>
+      <c r="L21" t="s">
+        <v>93</v>
+      </c>
+      <c r="M21" t="s">
+        <v>175</v>
+      </c>
+      <c r="N21" t="s">
         <v>176</v>
       </c>
-      <c r="K21" t="s">
-        <v>95</v>
-      </c>
-      <c r="L21" t="s">
-        <v>95</v>
-      </c>
-      <c r="M21" t="s">
-        <v>177</v>
-      </c>
-      <c r="N21" t="s">
-        <v>178</v>
-      </c>
       <c r="O21" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" ht="25.5" customHeight="1" spans="1:16">
@@ -5571,49 +5588,49 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
+        <v>166</v>
+      </c>
+      <c r="D22" t="s">
+        <v>200</v>
+      </c>
+      <c r="E22" t="s">
+        <v>167</v>
+      </c>
+      <c r="F22" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" t="s">
         <v>168</v>
       </c>
-      <c r="D22" t="s">
-        <v>202</v>
-      </c>
-      <c r="E22" t="s">
-        <v>169</v>
-      </c>
-      <c r="F22" t="s">
-        <v>49</v>
-      </c>
-      <c r="G22" t="s">
-        <v>170</v>
-      </c>
       <c r="H22" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I22" s="2">
         <v>46198</v>
       </c>
       <c r="J22" t="s">
+        <v>174</v>
+      </c>
+      <c r="K22" t="s">
+        <v>93</v>
+      </c>
+      <c r="L22" t="s">
+        <v>93</v>
+      </c>
+      <c r="M22" t="s">
+        <v>175</v>
+      </c>
+      <c r="N22" t="s">
         <v>176</v>
       </c>
-      <c r="K22" t="s">
-        <v>95</v>
-      </c>
-      <c r="L22" t="s">
-        <v>95</v>
-      </c>
-      <c r="M22" t="s">
-        <v>177</v>
-      </c>
-      <c r="N22" t="s">
-        <v>178</v>
-      </c>
       <c r="O22" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" ht="25.5" customHeight="1" spans="1:16">
@@ -5621,49 +5638,49 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
+        <v>166</v>
+      </c>
+      <c r="D23" t="s">
+        <v>201</v>
+      </c>
+      <c r="E23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G23" t="s">
         <v>168</v>
       </c>
-      <c r="D23" t="s">
-        <v>203</v>
-      </c>
-      <c r="E23" t="s">
-        <v>169</v>
-      </c>
-      <c r="F23" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23" t="s">
-        <v>170</v>
-      </c>
       <c r="H23" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I23" s="2">
         <v>46199</v>
       </c>
       <c r="J23" t="s">
+        <v>174</v>
+      </c>
+      <c r="K23" t="s">
+        <v>93</v>
+      </c>
+      <c r="L23" t="s">
+        <v>93</v>
+      </c>
+      <c r="M23" t="s">
+        <v>175</v>
+      </c>
+      <c r="N23" t="s">
         <v>176</v>
       </c>
-      <c r="K23" t="s">
-        <v>95</v>
-      </c>
-      <c r="L23" t="s">
-        <v>95</v>
-      </c>
-      <c r="M23" t="s">
-        <v>177</v>
-      </c>
-      <c r="N23" t="s">
-        <v>178</v>
-      </c>
       <c r="O23" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" ht="25.5" customHeight="1" spans="1:16">
@@ -5671,49 +5688,49 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" t="s">
+        <v>203</v>
+      </c>
+      <c r="E24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F24" t="s">
+        <v>47</v>
+      </c>
+      <c r="G24" t="s">
         <v>168</v>
       </c>
-      <c r="D24" t="s">
-        <v>205</v>
-      </c>
-      <c r="E24" t="s">
-        <v>169</v>
-      </c>
-      <c r="F24" t="s">
-        <v>49</v>
-      </c>
-      <c r="G24" t="s">
-        <v>170</v>
-      </c>
       <c r="H24" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I24" s="2">
         <v>46195</v>
       </c>
       <c r="J24" t="s">
+        <v>174</v>
+      </c>
+      <c r="K24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L24" t="s">
+        <v>51</v>
+      </c>
+      <c r="M24" t="s">
+        <v>170</v>
+      </c>
+      <c r="N24" t="s">
         <v>176</v>
       </c>
-      <c r="K24" t="s">
-        <v>53</v>
-      </c>
-      <c r="L24" t="s">
-        <v>53</v>
-      </c>
-      <c r="M24" t="s">
+      <c r="O24" t="s">
         <v>172</v>
       </c>
-      <c r="N24" t="s">
-        <v>178</v>
-      </c>
-      <c r="O24" t="s">
-        <v>174</v>
-      </c>
       <c r="P24" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" ht="25.5" customHeight="1" spans="1:16">
@@ -5721,49 +5738,49 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
+        <v>204</v>
+      </c>
+      <c r="D25" t="s">
+        <v>205</v>
+      </c>
+      <c r="E25" t="s">
         <v>206</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>207</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
+        <v>168</v>
+      </c>
+      <c r="H25" t="s">
         <v>208</v>
-      </c>
-      <c r="F25" t="s">
-        <v>209</v>
-      </c>
-      <c r="G25" t="s">
-        <v>170</v>
-      </c>
-      <c r="H25" t="s">
-        <v>210</v>
       </c>
       <c r="I25" s="2">
         <v>46209</v>
       </c>
       <c r="J25" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M25" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N25" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P25" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" ht="25.5" customHeight="1" spans="1:16">
@@ -5771,49 +5788,49 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D26" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E26" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F26" t="s">
         <v>29</v>
       </c>
       <c r="G26" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I26" s="2">
         <v>46204</v>
       </c>
       <c r="J26" t="s">
+        <v>174</v>
+      </c>
+      <c r="K26" t="s">
+        <v>79</v>
+      </c>
+      <c r="L26" t="s">
+        <v>79</v>
+      </c>
+      <c r="M26" t="s">
+        <v>175</v>
+      </c>
+      <c r="N26" t="s">
         <v>176</v>
       </c>
-      <c r="K26" t="s">
-        <v>81</v>
-      </c>
-      <c r="L26" t="s">
-        <v>81</v>
-      </c>
-      <c r="M26" t="s">
-        <v>177</v>
-      </c>
-      <c r="N26" t="s">
-        <v>178</v>
-      </c>
       <c r="O26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" ht="25.5" customHeight="1" spans="1:16">
@@ -5821,49 +5838,49 @@
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D27" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E27" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F27" t="s">
         <v>29</v>
       </c>
       <c r="G27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I27" s="2">
         <v>46204</v>
       </c>
       <c r="J27" t="s">
+        <v>174</v>
+      </c>
+      <c r="K27" t="s">
+        <v>79</v>
+      </c>
+      <c r="L27" t="s">
+        <v>79</v>
+      </c>
+      <c r="M27" t="s">
+        <v>175</v>
+      </c>
+      <c r="N27" t="s">
         <v>176</v>
       </c>
-      <c r="K27" t="s">
-        <v>81</v>
-      </c>
-      <c r="L27" t="s">
-        <v>81</v>
-      </c>
-      <c r="M27" t="s">
-        <v>177</v>
-      </c>
-      <c r="N27" t="s">
-        <v>178</v>
-      </c>
       <c r="O27" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" ht="25.5" customHeight="1" spans="1:16">
@@ -5871,49 +5888,49 @@
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C28" t="s">
+        <v>204</v>
+      </c>
+      <c r="D28" t="s">
+        <v>215</v>
+      </c>
+      <c r="E28" t="s">
         <v>206</v>
       </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
+        <v>216</v>
+      </c>
+      <c r="G28" t="s">
+        <v>168</v>
+      </c>
+      <c r="H28" t="s">
         <v>217</v>
-      </c>
-      <c r="E28" t="s">
-        <v>208</v>
-      </c>
-      <c r="F28" t="s">
-        <v>218</v>
-      </c>
-      <c r="G28" t="s">
-        <v>170</v>
-      </c>
-      <c r="H28" t="s">
-        <v>219</v>
       </c>
       <c r="I28" s="2">
         <v>46209</v>
       </c>
       <c r="J28" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K28" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L28" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M28" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N28" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P28" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" ht="25.5" customHeight="1" spans="1:16">
@@ -5921,49 +5938,49 @@
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
+        <v>204</v>
+      </c>
+      <c r="D29" t="s">
+        <v>218</v>
+      </c>
+      <c r="E29" t="s">
         <v>206</v>
       </c>
-      <c r="D29" t="s">
-        <v>220</v>
-      </c>
-      <c r="E29" t="s">
-        <v>208</v>
-      </c>
       <c r="F29" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G29" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H29" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I29" s="2">
         <v>46209</v>
       </c>
       <c r="J29" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M29" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N29" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" ht="25.5" customHeight="1" spans="1:16">
@@ -5971,49 +5988,49 @@
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
+        <v>204</v>
+      </c>
+      <c r="D30" t="s">
+        <v>219</v>
+      </c>
+      <c r="E30" t="s">
         <v>206</v>
       </c>
-      <c r="D30" t="s">
-        <v>221</v>
-      </c>
-      <c r="E30" t="s">
-        <v>208</v>
-      </c>
       <c r="F30" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G30" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H30" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I30" s="2">
         <v>46215</v>
       </c>
       <c r="J30" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M30" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N30" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" ht="25.5" customHeight="1" spans="1:16">
@@ -6021,49 +6038,49 @@
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
+        <v>204</v>
+      </c>
+      <c r="D31" t="s">
+        <v>220</v>
+      </c>
+      <c r="E31" t="s">
         <v>206</v>
       </c>
-      <c r="D31" t="s">
-        <v>222</v>
-      </c>
-      <c r="E31" t="s">
-        <v>208</v>
-      </c>
       <c r="F31" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G31" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H31" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I31" s="2">
         <v>46209</v>
       </c>
       <c r="J31" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M31" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N31" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O31" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P31" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" ht="25.5" customHeight="1" spans="1:16">
@@ -6071,49 +6088,49 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
+        <v>204</v>
+      </c>
+      <c r="D32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E32" t="s">
         <v>206</v>
       </c>
-      <c r="D32" t="s">
-        <v>224</v>
-      </c>
-      <c r="E32" t="s">
-        <v>208</v>
-      </c>
       <c r="F32" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G32" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H32" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I32" s="2">
         <v>46209</v>
       </c>
       <c r="J32" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M32" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N32" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O32" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" ht="25.5" customHeight="1" spans="1:16">
@@ -6121,49 +6138,49 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D33" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E33" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F33" t="s">
         <v>29</v>
       </c>
       <c r="G33" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H33" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I33" s="2">
         <v>46209</v>
       </c>
       <c r="J33" t="s">
+        <v>174</v>
+      </c>
+      <c r="K33" t="s">
+        <v>225</v>
+      </c>
+      <c r="L33" t="s">
+        <v>225</v>
+      </c>
+      <c r="M33" t="s">
+        <v>175</v>
+      </c>
+      <c r="N33" t="s">
         <v>176</v>
       </c>
-      <c r="K33" t="s">
-        <v>227</v>
-      </c>
-      <c r="L33" t="s">
-        <v>227</v>
-      </c>
-      <c r="M33" t="s">
-        <v>177</v>
-      </c>
-      <c r="N33" t="s">
-        <v>178</v>
-      </c>
       <c r="O33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P33" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" ht="25.5" customHeight="1" spans="1:16">
@@ -6171,49 +6188,49 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
+        <v>166</v>
+      </c>
+      <c r="D34" t="s">
+        <v>226</v>
+      </c>
+      <c r="E34" t="s">
+        <v>167</v>
+      </c>
+      <c r="F34" t="s">
+        <v>47</v>
+      </c>
+      <c r="G34" t="s">
         <v>168</v>
       </c>
-      <c r="D34" t="s">
-        <v>228</v>
-      </c>
-      <c r="E34" t="s">
-        <v>169</v>
-      </c>
-      <c r="F34" t="s">
-        <v>49</v>
-      </c>
-      <c r="G34" t="s">
-        <v>170</v>
-      </c>
       <c r="H34" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I34" s="2">
         <v>46204</v>
       </c>
       <c r="J34" t="s">
+        <v>174</v>
+      </c>
+      <c r="K34" t="s">
+        <v>93</v>
+      </c>
+      <c r="L34" t="s">
+        <v>93</v>
+      </c>
+      <c r="M34" t="s">
+        <v>175</v>
+      </c>
+      <c r="N34" t="s">
         <v>176</v>
       </c>
-      <c r="K34" t="s">
-        <v>95</v>
-      </c>
-      <c r="L34" t="s">
-        <v>95</v>
-      </c>
-      <c r="M34" t="s">
-        <v>177</v>
-      </c>
-      <c r="N34" t="s">
-        <v>178</v>
-      </c>
       <c r="O34" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" ht="25.5" customHeight="1" spans="1:16">
@@ -6221,49 +6238,49 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
+        <v>204</v>
+      </c>
+      <c r="D35" t="s">
+        <v>227</v>
+      </c>
+      <c r="E35" t="s">
         <v>206</v>
       </c>
-      <c r="D35" t="s">
-        <v>229</v>
-      </c>
-      <c r="E35" t="s">
-        <v>208</v>
-      </c>
       <c r="F35" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H35" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I35" s="2">
         <v>46209</v>
       </c>
       <c r="J35" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M35" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N35" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O35" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P35" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" ht="25.5" customHeight="1" spans="1:16">
@@ -6271,49 +6288,49 @@
         <v>86</v>
       </c>
       <c r="B36" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C36" t="s">
+        <v>166</v>
+      </c>
+      <c r="D36" t="s">
+        <v>228</v>
+      </c>
+      <c r="E36" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36" t="s">
+        <v>47</v>
+      </c>
+      <c r="G36" t="s">
         <v>168</v>
       </c>
-      <c r="D36" t="s">
-        <v>230</v>
-      </c>
-      <c r="E36" t="s">
-        <v>169</v>
-      </c>
-      <c r="F36" t="s">
-        <v>49</v>
-      </c>
-      <c r="G36" t="s">
-        <v>170</v>
-      </c>
       <c r="H36" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I36" s="2">
         <v>46209</v>
       </c>
       <c r="J36" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K36" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L36" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M36" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N36" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O36" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P36" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" ht="25.5" customHeight="1" spans="1:16">
@@ -6321,49 +6338,49 @@
         <v>115</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
+        <v>166</v>
+      </c>
+      <c r="D37" t="s">
+        <v>230</v>
+      </c>
+      <c r="E37" t="s">
+        <v>167</v>
+      </c>
+      <c r="F37" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37" t="s">
         <v>168</v>
       </c>
-      <c r="D37" t="s">
-        <v>232</v>
-      </c>
-      <c r="E37" t="s">
-        <v>169</v>
-      </c>
-      <c r="F37" t="s">
-        <v>49</v>
-      </c>
-      <c r="G37" t="s">
-        <v>170</v>
-      </c>
       <c r="H37" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I37" s="2">
         <v>46224</v>
       </c>
       <c r="J37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K37" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L37" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M37" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N37" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O37" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P37" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" ht="25.5" customHeight="1" spans="1:16">
@@ -6371,49 +6388,49 @@
         <v>116</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D38" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E38" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F38" t="s">
         <v>29</v>
       </c>
       <c r="G38" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H38" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I38" s="2">
         <v>46209</v>
       </c>
       <c r="J38" t="s">
+        <v>174</v>
+      </c>
+      <c r="K38" t="s">
+        <v>79</v>
+      </c>
+      <c r="L38" t="s">
+        <v>79</v>
+      </c>
+      <c r="M38" t="s">
+        <v>175</v>
+      </c>
+      <c r="N38" t="s">
         <v>176</v>
       </c>
-      <c r="K38" t="s">
-        <v>81</v>
-      </c>
-      <c r="L38" t="s">
-        <v>81</v>
-      </c>
-      <c r="M38" t="s">
-        <v>177</v>
-      </c>
-      <c r="N38" t="s">
-        <v>178</v>
-      </c>
       <c r="O38" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P38" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" ht="25.5" customHeight="1" spans="1:16">
@@ -6421,49 +6438,49 @@
         <v>117</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C39" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D39" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E39" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F39" t="s">
         <v>29</v>
       </c>
       <c r="G39" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H39" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I39" s="2">
         <v>46209</v>
       </c>
       <c r="J39" t="s">
+        <v>174</v>
+      </c>
+      <c r="K39" t="s">
+        <v>79</v>
+      </c>
+      <c r="L39" t="s">
+        <v>79</v>
+      </c>
+      <c r="M39" t="s">
+        <v>175</v>
+      </c>
+      <c r="N39" t="s">
         <v>176</v>
       </c>
-      <c r="K39" t="s">
-        <v>81</v>
-      </c>
-      <c r="L39" t="s">
-        <v>81</v>
-      </c>
-      <c r="M39" t="s">
-        <v>177</v>
-      </c>
-      <c r="N39" t="s">
-        <v>178</v>
-      </c>
       <c r="O39" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P39" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" ht="25.5" customHeight="1" spans="1:16">
@@ -6471,49 +6488,49 @@
         <v>118</v>
       </c>
       <c r="B40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C40" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D40" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E40" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F40" t="s">
         <v>29</v>
       </c>
       <c r="G40" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H40" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I40" s="2">
         <v>46209</v>
       </c>
       <c r="J40" t="s">
+        <v>174</v>
+      </c>
+      <c r="K40" t="s">
+        <v>79</v>
+      </c>
+      <c r="L40" t="s">
+        <v>79</v>
+      </c>
+      <c r="M40" t="s">
+        <v>175</v>
+      </c>
+      <c r="N40" t="s">
         <v>176</v>
       </c>
-      <c r="K40" t="s">
-        <v>81</v>
-      </c>
-      <c r="L40" t="s">
-        <v>81</v>
-      </c>
-      <c r="M40" t="s">
-        <v>177</v>
-      </c>
-      <c r="N40" t="s">
-        <v>178</v>
-      </c>
       <c r="O40" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P40" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" ht="25.5" customHeight="1" spans="1:16">
@@ -6521,49 +6538,49 @@
         <v>119</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C41" t="s">
+        <v>166</v>
+      </c>
+      <c r="D41" t="s">
+        <v>234</v>
+      </c>
+      <c r="E41" t="s">
+        <v>167</v>
+      </c>
+      <c r="F41" t="s">
+        <v>47</v>
+      </c>
+      <c r="G41" t="s">
         <v>168</v>
       </c>
-      <c r="D41" t="s">
-        <v>236</v>
-      </c>
-      <c r="E41" t="s">
-        <v>169</v>
-      </c>
-      <c r="F41" t="s">
-        <v>49</v>
-      </c>
-      <c r="G41" t="s">
-        <v>170</v>
-      </c>
       <c r="H41" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I41" s="2">
         <v>46210</v>
       </c>
       <c r="J41" t="s">
+        <v>174</v>
+      </c>
+      <c r="K41" t="s">
+        <v>93</v>
+      </c>
+      <c r="L41" t="s">
+        <v>93</v>
+      </c>
+      <c r="M41" t="s">
+        <v>175</v>
+      </c>
+      <c r="N41" t="s">
         <v>176</v>
       </c>
-      <c r="K41" t="s">
-        <v>95</v>
-      </c>
-      <c r="L41" t="s">
-        <v>95</v>
-      </c>
-      <c r="M41" t="s">
-        <v>177</v>
-      </c>
-      <c r="N41" t="s">
-        <v>178</v>
-      </c>
       <c r="O41" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P41" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" ht="25.5" customHeight="1" spans="1:16">
@@ -6571,49 +6588,49 @@
         <v>120</v>
       </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C42" t="s">
+        <v>166</v>
+      </c>
+      <c r="D42" t="s">
+        <v>235</v>
+      </c>
+      <c r="E42" t="s">
+        <v>167</v>
+      </c>
+      <c r="F42" t="s">
+        <v>47</v>
+      </c>
+      <c r="G42" t="s">
         <v>168</v>
       </c>
-      <c r="D42" t="s">
-        <v>237</v>
-      </c>
-      <c r="E42" t="s">
-        <v>169</v>
-      </c>
-      <c r="F42" t="s">
-        <v>49</v>
-      </c>
-      <c r="G42" t="s">
-        <v>170</v>
-      </c>
       <c r="H42" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I42" s="2">
         <v>46209</v>
       </c>
       <c r="J42" t="s">
+        <v>174</v>
+      </c>
+      <c r="K42" t="s">
+        <v>93</v>
+      </c>
+      <c r="L42" t="s">
+        <v>93</v>
+      </c>
+      <c r="M42" t="s">
+        <v>175</v>
+      </c>
+      <c r="N42" t="s">
         <v>176</v>
       </c>
-      <c r="K42" t="s">
-        <v>95</v>
-      </c>
-      <c r="L42" t="s">
-        <v>95</v>
-      </c>
-      <c r="M42" t="s">
-        <v>177</v>
-      </c>
-      <c r="N42" t="s">
-        <v>178</v>
-      </c>
       <c r="O42" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P42" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" ht="25.5" customHeight="1" spans="1:16">
@@ -6624,46 +6641,46 @@
         <v>33</v>
       </c>
       <c r="C43" t="s">
+        <v>204</v>
+      </c>
+      <c r="D43" t="s">
+        <v>236</v>
+      </c>
+      <c r="E43" t="s">
         <v>206</v>
       </c>
-      <c r="D43" t="s">
-        <v>238</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
+        <v>237</v>
+      </c>
+      <c r="G43" t="s">
+        <v>168</v>
+      </c>
+      <c r="H43" t="s">
         <v>208</v>
-      </c>
-      <c r="F43" t="s">
-        <v>239</v>
-      </c>
-      <c r="G43" t="s">
-        <v>170</v>
-      </c>
-      <c r="H43" t="s">
-        <v>210</v>
       </c>
       <c r="I43" s="2">
         <v>46216</v>
       </c>
       <c r="J43" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K43" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L43" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M43" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N43" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P43" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="44" ht="25.5" customHeight="1" spans="1:16">
@@ -6671,49 +6688,49 @@
         <v>123</v>
       </c>
       <c r="B44" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C44" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D44" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E44" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F44" t="s">
         <v>29</v>
       </c>
       <c r="G44" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H44" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I44" s="2">
         <v>46210</v>
       </c>
       <c r="J44" t="s">
+        <v>174</v>
+      </c>
+      <c r="K44" t="s">
+        <v>86</v>
+      </c>
+      <c r="L44" t="s">
+        <v>86</v>
+      </c>
+      <c r="M44" t="s">
+        <v>175</v>
+      </c>
+      <c r="N44" t="s">
         <v>176</v>
       </c>
-      <c r="K44" t="s">
-        <v>88</v>
-      </c>
-      <c r="L44" t="s">
-        <v>88</v>
-      </c>
-      <c r="M44" t="s">
-        <v>177</v>
-      </c>
-      <c r="N44" t="s">
-        <v>178</v>
-      </c>
       <c r="O44" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P44" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" ht="25.5" customHeight="1" spans="1:16">
@@ -6721,49 +6738,49 @@
         <v>124</v>
       </c>
       <c r="B45" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C45" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D45" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E45" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F45" t="s">
         <v>29</v>
       </c>
       <c r="G45" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H45" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I45" s="2">
         <v>46210</v>
       </c>
       <c r="J45" t="s">
+        <v>174</v>
+      </c>
+      <c r="K45" t="s">
+        <v>86</v>
+      </c>
+      <c r="L45" t="s">
+        <v>86</v>
+      </c>
+      <c r="M45" t="s">
+        <v>175</v>
+      </c>
+      <c r="N45" t="s">
         <v>176</v>
       </c>
-      <c r="K45" t="s">
-        <v>88</v>
-      </c>
-      <c r="L45" t="s">
-        <v>88</v>
-      </c>
-      <c r="M45" t="s">
-        <v>177</v>
-      </c>
-      <c r="N45" t="s">
-        <v>178</v>
-      </c>
       <c r="O45" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P45" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" ht="25.5" customHeight="1" spans="1:16">
@@ -6771,49 +6788,49 @@
         <v>125</v>
       </c>
       <c r="B46" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C46" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D46" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E46" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F46" t="s">
         <v>29</v>
       </c>
       <c r="G46" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H46" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I46" s="2">
         <v>46210</v>
       </c>
       <c r="J46" t="s">
+        <v>174</v>
+      </c>
+      <c r="K46" t="s">
+        <v>86</v>
+      </c>
+      <c r="L46" t="s">
+        <v>86</v>
+      </c>
+      <c r="M46" t="s">
+        <v>175</v>
+      </c>
+      <c r="N46" t="s">
         <v>176</v>
       </c>
-      <c r="K46" t="s">
-        <v>88</v>
-      </c>
-      <c r="L46" t="s">
-        <v>88</v>
-      </c>
-      <c r="M46" t="s">
-        <v>177</v>
-      </c>
-      <c r="N46" t="s">
-        <v>178</v>
-      </c>
       <c r="O46" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P46" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" ht="25.5" customHeight="1" spans="1:16">
@@ -6821,49 +6838,49 @@
         <v>126</v>
       </c>
       <c r="B47" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C47" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D47" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F47" t="s">
         <v>29</v>
       </c>
       <c r="G47" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H47" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I47" s="2">
         <v>46210</v>
       </c>
       <c r="J47" t="s">
+        <v>174</v>
+      </c>
+      <c r="K47" t="s">
+        <v>86</v>
+      </c>
+      <c r="L47" t="s">
+        <v>86</v>
+      </c>
+      <c r="M47" t="s">
+        <v>175</v>
+      </c>
+      <c r="N47" t="s">
         <v>176</v>
       </c>
-      <c r="K47" t="s">
-        <v>88</v>
-      </c>
-      <c r="L47" t="s">
-        <v>88</v>
-      </c>
-      <c r="M47" t="s">
-        <v>177</v>
-      </c>
-      <c r="N47" t="s">
-        <v>178</v>
-      </c>
       <c r="O47" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P47" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" ht="25.5" customHeight="1" spans="1:16">
@@ -6871,49 +6888,49 @@
         <v>127</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C48" t="s">
+        <v>204</v>
+      </c>
+      <c r="D48" t="s">
+        <v>244</v>
+      </c>
+      <c r="E48" t="s">
         <v>206</v>
       </c>
-      <c r="D48" t="s">
-        <v>246</v>
-      </c>
-      <c r="E48" t="s">
-        <v>208</v>
-      </c>
       <c r="F48" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G48" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H48" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I48" s="2">
         <v>46213</v>
       </c>
       <c r="J48" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K48" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L48" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M48" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N48" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O48" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" ht="25.5" customHeight="1" spans="1:16">
@@ -6921,49 +6938,49 @@
         <v>128</v>
       </c>
       <c r="B49" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C49" t="s">
+        <v>204</v>
+      </c>
+      <c r="D49" t="s">
+        <v>245</v>
+      </c>
+      <c r="E49" t="s">
         <v>206</v>
       </c>
-      <c r="D49" t="s">
-        <v>247</v>
-      </c>
-      <c r="E49" t="s">
-        <v>208</v>
-      </c>
       <c r="F49" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G49" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H49" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I49" s="2">
         <v>46213</v>
       </c>
       <c r="J49" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K49" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L49" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N49" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O49" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" ht="25.5" customHeight="1" spans="1:16">
@@ -6971,47 +6988,47 @@
         <v>129</v>
       </c>
       <c r="B50" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C50" t="s">
+        <v>204</v>
+      </c>
+      <c r="D50" t="s">
+        <v>246</v>
+      </c>
+      <c r="E50" t="s">
         <v>206</v>
       </c>
-      <c r="D50" t="s">
-        <v>248</v>
-      </c>
-      <c r="E50" t="s">
-        <v>208</v>
-      </c>
       <c r="F50" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G50" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H50" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K50" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L50" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M50" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N50" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O50" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" ht="25.5" customHeight="1" spans="1:16">
@@ -7019,47 +7036,47 @@
         <v>130</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C51" t="s">
+        <v>204</v>
+      </c>
+      <c r="D51" t="s">
+        <v>247</v>
+      </c>
+      <c r="E51" t="s">
         <v>206</v>
       </c>
-      <c r="D51" t="s">
-        <v>249</v>
-      </c>
-      <c r="E51" t="s">
-        <v>208</v>
-      </c>
       <c r="F51" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G51" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H51" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K51" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L51" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M51" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N51" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O51" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P51" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" ht="25.5" customHeight="1" spans="1:16">
@@ -7067,47 +7084,47 @@
         <v>131</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C52" t="s">
+        <v>204</v>
+      </c>
+      <c r="D52" t="s">
+        <v>248</v>
+      </c>
+      <c r="E52" t="s">
         <v>206</v>
       </c>
-      <c r="D52" t="s">
-        <v>250</v>
-      </c>
-      <c r="E52" t="s">
-        <v>208</v>
-      </c>
       <c r="F52" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G52" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H52" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K52" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L52" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M52" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N52" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O52" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" ht="25.5" customHeight="1" spans="1:16">
@@ -7115,49 +7132,49 @@
         <v>132</v>
       </c>
       <c r="B53" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C53" t="s">
+        <v>166</v>
+      </c>
+      <c r="D53" t="s">
+        <v>249</v>
+      </c>
+      <c r="E53" t="s">
+        <v>167</v>
+      </c>
+      <c r="F53" t="s">
+        <v>47</v>
+      </c>
+      <c r="G53" t="s">
         <v>168</v>
       </c>
-      <c r="D53" t="s">
-        <v>251</v>
-      </c>
-      <c r="E53" t="s">
-        <v>169</v>
-      </c>
-      <c r="F53" t="s">
-        <v>49</v>
-      </c>
-      <c r="G53" t="s">
-        <v>170</v>
-      </c>
       <c r="H53" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I53" s="2">
         <v>46216</v>
       </c>
       <c r="J53" t="s">
+        <v>174</v>
+      </c>
+      <c r="K53" t="s">
+        <v>93</v>
+      </c>
+      <c r="L53" t="s">
+        <v>93</v>
+      </c>
+      <c r="M53" t="s">
+        <v>175</v>
+      </c>
+      <c r="N53" t="s">
         <v>176</v>
       </c>
-      <c r="K53" t="s">
-        <v>95</v>
-      </c>
-      <c r="L53" t="s">
-        <v>95</v>
-      </c>
-      <c r="M53" t="s">
-        <v>177</v>
-      </c>
-      <c r="N53" t="s">
-        <v>178</v>
-      </c>
       <c r="O53" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P53" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" ht="25.5" customHeight="1" spans="1:16">
@@ -7165,49 +7182,49 @@
         <v>133</v>
       </c>
       <c r="B54" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C54" t="s">
+        <v>166</v>
+      </c>
+      <c r="D54" t="s">
+        <v>250</v>
+      </c>
+      <c r="E54" t="s">
+        <v>167</v>
+      </c>
+      <c r="F54" t="s">
+        <v>47</v>
+      </c>
+      <c r="G54" t="s">
         <v>168</v>
       </c>
-      <c r="D54" t="s">
-        <v>252</v>
-      </c>
-      <c r="E54" t="s">
-        <v>169</v>
-      </c>
-      <c r="F54" t="s">
-        <v>49</v>
-      </c>
-      <c r="G54" t="s">
-        <v>170</v>
-      </c>
       <c r="H54" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I54" s="2">
         <v>46216</v>
       </c>
       <c r="J54" t="s">
+        <v>174</v>
+      </c>
+      <c r="K54" t="s">
+        <v>93</v>
+      </c>
+      <c r="L54" t="s">
+        <v>93</v>
+      </c>
+      <c r="M54" t="s">
+        <v>175</v>
+      </c>
+      <c r="N54" t="s">
         <v>176</v>
       </c>
-      <c r="K54" t="s">
-        <v>95</v>
-      </c>
-      <c r="L54" t="s">
-        <v>95</v>
-      </c>
-      <c r="M54" t="s">
-        <v>177</v>
-      </c>
-      <c r="N54" t="s">
-        <v>178</v>
-      </c>
       <c r="O54" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P54" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" ht="25.5" customHeight="1" spans="1:16">
@@ -7215,49 +7232,49 @@
         <v>134</v>
       </c>
       <c r="B55" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C55" t="s">
+        <v>166</v>
+      </c>
+      <c r="D55" t="s">
+        <v>251</v>
+      </c>
+      <c r="E55" t="s">
+        <v>167</v>
+      </c>
+      <c r="F55" t="s">
+        <v>47</v>
+      </c>
+      <c r="G55" t="s">
         <v>168</v>
       </c>
-      <c r="D55" t="s">
-        <v>253</v>
-      </c>
-      <c r="E55" t="s">
-        <v>169</v>
-      </c>
-      <c r="F55" t="s">
-        <v>49</v>
-      </c>
-      <c r="G55" t="s">
-        <v>170</v>
-      </c>
       <c r="H55" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I55" s="2">
         <v>46216</v>
       </c>
       <c r="J55" t="s">
+        <v>174</v>
+      </c>
+      <c r="K55" t="s">
+        <v>93</v>
+      </c>
+      <c r="L55" t="s">
+        <v>93</v>
+      </c>
+      <c r="M55" t="s">
+        <v>175</v>
+      </c>
+      <c r="N55" t="s">
         <v>176</v>
       </c>
-      <c r="K55" t="s">
-        <v>95</v>
-      </c>
-      <c r="L55" t="s">
-        <v>95</v>
-      </c>
-      <c r="M55" t="s">
-        <v>177</v>
-      </c>
-      <c r="N55" t="s">
-        <v>178</v>
-      </c>
       <c r="O55" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P55" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" ht="25.5" customHeight="1" spans="1:16">
@@ -7265,49 +7282,49 @@
         <v>135</v>
       </c>
       <c r="B56" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C56" t="s">
+        <v>166</v>
+      </c>
+      <c r="D56" t="s">
+        <v>252</v>
+      </c>
+      <c r="E56" t="s">
+        <v>167</v>
+      </c>
+      <c r="F56" t="s">
+        <v>47</v>
+      </c>
+      <c r="G56" t="s">
         <v>168</v>
       </c>
-      <c r="D56" t="s">
-        <v>254</v>
-      </c>
-      <c r="E56" t="s">
-        <v>169</v>
-      </c>
-      <c r="F56" t="s">
-        <v>49</v>
-      </c>
-      <c r="G56" t="s">
-        <v>170</v>
-      </c>
       <c r="H56" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I56" s="2">
         <v>46216</v>
       </c>
       <c r="J56" t="s">
+        <v>174</v>
+      </c>
+      <c r="K56" t="s">
+        <v>93</v>
+      </c>
+      <c r="L56" t="s">
+        <v>93</v>
+      </c>
+      <c r="M56" t="s">
+        <v>175</v>
+      </c>
+      <c r="N56" t="s">
         <v>176</v>
       </c>
-      <c r="K56" t="s">
-        <v>95</v>
-      </c>
-      <c r="L56" t="s">
-        <v>95</v>
-      </c>
-      <c r="M56" t="s">
-        <v>177</v>
-      </c>
-      <c r="N56" t="s">
-        <v>178</v>
-      </c>
       <c r="O56" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P56" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" ht="25.5" customHeight="1" spans="1:16">
@@ -7315,49 +7332,49 @@
         <v>136</v>
       </c>
       <c r="B57" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C57" t="s">
+        <v>166</v>
+      </c>
+      <c r="D57" t="s">
+        <v>253</v>
+      </c>
+      <c r="E57" t="s">
+        <v>167</v>
+      </c>
+      <c r="F57" t="s">
+        <v>47</v>
+      </c>
+      <c r="G57" t="s">
         <v>168</v>
       </c>
-      <c r="D57" t="s">
-        <v>255</v>
-      </c>
-      <c r="E57" t="s">
-        <v>169</v>
-      </c>
-      <c r="F57" t="s">
-        <v>49</v>
-      </c>
-      <c r="G57" t="s">
-        <v>170</v>
-      </c>
       <c r="H57" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I57" s="2">
         <v>46216</v>
       </c>
       <c r="J57" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K57" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L57" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M57" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N57" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O57" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P57" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" ht="25.5" customHeight="1" spans="1:16">
@@ -7365,49 +7382,49 @@
         <v>137</v>
       </c>
       <c r="B58" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C58" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D58" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E58" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F58" t="s">
         <v>29</v>
       </c>
       <c r="G58" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H58" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I58" s="2">
         <v>46216</v>
       </c>
       <c r="J58" t="s">
+        <v>174</v>
+      </c>
+      <c r="K58" t="s">
+        <v>181</v>
+      </c>
+      <c r="L58" t="s">
+        <v>181</v>
+      </c>
+      <c r="M58" t="s">
+        <v>175</v>
+      </c>
+      <c r="N58" t="s">
         <v>176</v>
       </c>
-      <c r="K58" t="s">
-        <v>183</v>
-      </c>
-      <c r="L58" t="s">
-        <v>183</v>
-      </c>
-      <c r="M58" t="s">
-        <v>177</v>
-      </c>
-      <c r="N58" t="s">
-        <v>178</v>
-      </c>
       <c r="O58" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P58" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -7459,40 +7476,40 @@
   <sheetData>
     <row r="1" ht="13" customHeight="1" spans="1:13">
       <c r="A1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>271</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>10</v>
@@ -7503,13 +7520,13 @@
         <v>46198</v>
       </c>
       <c r="B2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2" t="s">
         <v>219</v>
       </c>
-      <c r="C2" t="s">
-        <v>221</v>
-      </c>
       <c r="E2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F2">
         <v>26</v>
@@ -7518,22 +7535,22 @@
         <v>18231062662</v>
       </c>
       <c r="H2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I2" t="s">
+        <v>272</v>
+      </c>
+      <c r="J2" t="s">
         <v>273</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L2" t="s">
         <v>274</v>
       </c>
-      <c r="J2" t="s">
-        <v>275</v>
-      </c>
-      <c r="K2" t="s">
-        <v>168</v>
-      </c>
-      <c r="L2" t="s">
-        <v>276</v>
-      </c>
       <c r="M2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" ht="25.5" customHeight="1" spans="1:13">
@@ -7541,13 +7558,13 @@
         <v>46198</v>
       </c>
       <c r="B3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F3">
         <v>19</v>
@@ -7556,22 +7573,22 @@
         <v>13162929052</v>
       </c>
       <c r="H3" t="s">
+        <v>275</v>
+      </c>
+      <c r="I3" t="s">
+        <v>276</v>
+      </c>
+      <c r="J3" t="s">
         <v>277</v>
       </c>
-      <c r="I3" t="s">
-        <v>278</v>
-      </c>
-      <c r="J3" t="s">
-        <v>279</v>
-      </c>
       <c r="K3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" ht="25.5" customHeight="1" spans="1:13">
@@ -7579,13 +7596,13 @@
         <v>46198</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F4">
         <v>33</v>
@@ -7594,22 +7611,22 @@
         <v>18382779439</v>
       </c>
       <c r="H4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" ht="25.5" customHeight="1" spans="1:13">
@@ -7617,13 +7634,13 @@
         <v>46198</v>
       </c>
       <c r="B5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F5">
         <v>34</v>
@@ -7632,22 +7649,22 @@
         <v>13916208405</v>
       </c>
       <c r="H5" t="s">
+        <v>279</v>
+      </c>
+      <c r="I5" t="s">
+        <v>276</v>
+      </c>
+      <c r="J5" t="s">
         <v>281</v>
       </c>
-      <c r="I5" t="s">
-        <v>278</v>
-      </c>
-      <c r="J5" t="s">
-        <v>283</v>
-      </c>
       <c r="K5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" ht="25.5" customHeight="1" spans="1:13">
@@ -7655,13 +7672,13 @@
         <v>46198</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F6">
         <v>23</v>
@@ -7670,19 +7687,19 @@
         <v>18013087603</v>
       </c>
       <c r="I6" t="s">
+        <v>283</v>
+      </c>
+      <c r="J6" t="s">
+        <v>284</v>
+      </c>
+      <c r="K6" t="s">
+        <v>166</v>
+      </c>
+      <c r="L6" t="s">
         <v>285</v>
       </c>
-      <c r="J6" t="s">
-        <v>286</v>
-      </c>
-      <c r="K6" t="s">
-        <v>168</v>
-      </c>
-      <c r="L6" t="s">
-        <v>287</v>
-      </c>
       <c r="M6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="25.5" customHeight="1" spans="1:13">
@@ -7690,13 +7707,13 @@
         <v>46198</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F7">
         <v>28</v>
@@ -7705,19 +7722,19 @@
         <v>15297141987</v>
       </c>
       <c r="I7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="K7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" ht="25.5" customHeight="1" spans="1:13">
@@ -7725,13 +7742,13 @@
         <v>46199</v>
       </c>
       <c r="B8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F8">
         <v>44</v>
@@ -7740,22 +7757,22 @@
         <v>13917228109</v>
       </c>
       <c r="H8" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="K8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" ht="25.5" customHeight="1" spans="1:13">
@@ -7763,13 +7780,13 @@
         <v>46199</v>
       </c>
       <c r="B9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C9" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F9">
         <v>36</v>
@@ -7778,22 +7795,22 @@
         <v>18221536383</v>
       </c>
       <c r="H9" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I9" t="s">
+        <v>283</v>
+      </c>
+      <c r="J9" t="s">
+        <v>291</v>
+      </c>
+      <c r="K9" t="s">
+        <v>166</v>
+      </c>
+      <c r="L9" t="s">
         <v>285</v>
       </c>
-      <c r="J9" t="s">
-        <v>293</v>
-      </c>
-      <c r="K9" t="s">
-        <v>168</v>
-      </c>
-      <c r="L9" t="s">
-        <v>287</v>
-      </c>
       <c r="M9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" ht="25.5" customHeight="1" spans="1:13">
@@ -7801,13 +7818,13 @@
         <v>46199</v>
       </c>
       <c r="B10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F10">
         <v>41</v>
@@ -7816,19 +7833,19 @@
         <v>18117003164</v>
       </c>
       <c r="H10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J10" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M10" t="s">
         <v>33</v>
@@ -7839,13 +7856,13 @@
         <v>46199</v>
       </c>
       <c r="B11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E11" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F11">
         <v>31</v>
@@ -7854,19 +7871,19 @@
         <v>15821995510</v>
       </c>
       <c r="H11" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I11" t="s">
+        <v>283</v>
+      </c>
+      <c r="J11" t="s">
+        <v>296</v>
+      </c>
+      <c r="K11" t="s">
+        <v>166</v>
+      </c>
+      <c r="L11" t="s">
         <v>285</v>
-      </c>
-      <c r="J11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K11" t="s">
-        <v>168</v>
-      </c>
-      <c r="L11" t="s">
-        <v>287</v>
       </c>
       <c r="M11" t="s">
         <v>33</v>
@@ -7877,13 +7894,13 @@
         <v>46199</v>
       </c>
       <c r="B12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F12">
         <v>33</v>
@@ -7892,16 +7909,16 @@
         <v>15618680171</v>
       </c>
       <c r="H12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L12" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M12" t="s">
         <v>33</v>
@@ -7912,16 +7929,16 @@
         <v>46199</v>
       </c>
       <c r="B13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D13" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E13" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F13">
         <v>28</v>
@@ -7930,22 +7947,22 @@
         <v>18049079692</v>
       </c>
       <c r="H13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I13" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J13" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="K13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L13" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" ht="25.5" customHeight="1" spans="1:13">
@@ -7953,13 +7970,13 @@
         <v>46199</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C14" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E14" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F14">
         <v>32</v>
@@ -7968,19 +7985,19 @@
         <v>18367738289</v>
       </c>
       <c r="I14" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J14" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="K14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L14" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="25.5" customHeight="1" spans="1:13">
@@ -7988,13 +8005,13 @@
         <v>46199</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E15" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F15">
         <v>25</v>
@@ -8003,19 +8020,19 @@
         <v>18638728837</v>
       </c>
       <c r="I15" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J15" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="K15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L15" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" ht="25.5" customHeight="1" spans="1:13">
@@ -8023,13 +8040,13 @@
         <v>46199</v>
       </c>
       <c r="B16" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C16" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E16" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F16">
         <v>29</v>
@@ -8038,19 +8055,19 @@
         <v>15956799150</v>
       </c>
       <c r="I16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J16" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="K16" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L16" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" ht="25.5" customHeight="1" spans="1:13">
@@ -8058,13 +8075,13 @@
         <v>46199</v>
       </c>
       <c r="B17" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C17" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E17" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F17">
         <v>29</v>
@@ -8073,19 +8090,19 @@
         <v>13761700050</v>
       </c>
       <c r="I17" t="s">
+        <v>303</v>
+      </c>
+      <c r="J17" t="s">
         <v>305</v>
       </c>
-      <c r="J17" t="s">
-        <v>307</v>
-      </c>
       <c r="K17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L17" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" ht="25.5" customHeight="1" spans="1:13">
@@ -8093,13 +8110,13 @@
         <v>46199</v>
       </c>
       <c r="B18" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C18" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E18" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F18">
         <v>24</v>
@@ -8108,19 +8125,19 @@
         <v>1843810022</v>
       </c>
       <c r="I18" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J18" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K18" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" ht="25.5" customHeight="1" spans="1:13">
@@ -8128,13 +8145,13 @@
         <v>46202</v>
       </c>
       <c r="B19" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E19" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F19">
         <v>25</v>
@@ -8143,22 +8160,22 @@
         <v>13145686593</v>
       </c>
       <c r="H19" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I19" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J19" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L19" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" ht="25.5" customHeight="1" spans="1:13">
@@ -8166,16 +8183,16 @@
         <v>46202</v>
       </c>
       <c r="B20" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C20" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D20" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F20">
         <v>26</v>
@@ -8184,22 +8201,22 @@
         <v>18770085531</v>
       </c>
       <c r="H20" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I20" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J20" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="K20" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" ht="25.5" customHeight="1" spans="1:13">
@@ -8207,13 +8224,13 @@
         <v>46203</v>
       </c>
       <c r="B21" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C21" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E21" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F21">
         <v>27</v>
@@ -8222,19 +8239,19 @@
         <v>17356025131</v>
       </c>
       <c r="H21" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I21" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K21" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L21" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M21" t="s">
         <v>33</v>
@@ -8245,13 +8262,13 @@
         <v>46203</v>
       </c>
       <c r="B22" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C22" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E22" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F22">
         <v>41</v>
@@ -8260,19 +8277,19 @@
         <v>18964903645</v>
       </c>
       <c r="H22" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I22" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J22" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K22" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L22" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M22" t="s">
         <v>33</v>
@@ -8283,16 +8300,16 @@
         <v>46203</v>
       </c>
       <c r="B23" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C23" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D23" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E23" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F23">
         <v>26</v>
@@ -8301,22 +8318,22 @@
         <v>18793321015</v>
       </c>
       <c r="H23" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I23" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J23" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="K23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L23" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" ht="25.5" customHeight="1" spans="1:13">
@@ -8324,13 +8341,13 @@
         <v>46203</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E24" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F24">
         <v>23</v>
@@ -8339,19 +8356,19 @@
         <v>18217695642</v>
       </c>
       <c r="I24" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J24" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K24" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L24" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" ht="25.5" customHeight="1" spans="1:13">
@@ -8359,13 +8376,13 @@
         <v>46203</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E25" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F25">
         <v>33</v>
@@ -8374,19 +8391,19 @@
         <v>15201704954</v>
       </c>
       <c r="I25" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J25" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K25" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L25" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" ht="25.5" customHeight="1" spans="1:13">
@@ -8394,13 +8411,13 @@
         <v>46206</v>
       </c>
       <c r="B26" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C26" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E26" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F26">
         <v>39</v>
@@ -8409,22 +8426,22 @@
         <v>13817304473</v>
       </c>
       <c r="H26" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I26" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J26" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="K26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L26" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" ht="25.5" customHeight="1" spans="1:13">
@@ -8432,13 +8449,13 @@
         <v>46210</v>
       </c>
       <c r="B27" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C27" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E27" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F27">
         <v>31</v>
@@ -8447,22 +8464,22 @@
         <v>15900469716</v>
       </c>
       <c r="H27" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I27" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J27" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K27" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L27" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" ht="25.5" customHeight="1" spans="1:13">
@@ -8470,13 +8487,13 @@
         <v>46210</v>
       </c>
       <c r="B28" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C28" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E28" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F28">
         <v>37</v>
@@ -8485,22 +8502,22 @@
         <v>18075905079</v>
       </c>
       <c r="H28" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I28" t="s">
+        <v>321</v>
+      </c>
+      <c r="J28" t="s">
         <v>323</v>
       </c>
-      <c r="J28" t="s">
-        <v>325</v>
-      </c>
       <c r="K28" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L28" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M28" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" ht="25.5" customHeight="1" spans="1:13">
@@ -8508,13 +8525,13 @@
         <v>46210</v>
       </c>
       <c r="B29" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C29" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E29" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F29">
         <v>27</v>
@@ -8523,22 +8540,22 @@
         <v>18217598368</v>
       </c>
       <c r="H29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I29" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J29" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K29" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L29" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" ht="25.5" customHeight="1" spans="1:13">
@@ -8546,13 +8563,13 @@
         <v>46211</v>
       </c>
       <c r="B30" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C30" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E30" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F30">
         <v>26</v>
@@ -8561,22 +8578,22 @@
         <v>16620794428</v>
       </c>
       <c r="H30" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I30" t="s">
+        <v>324</v>
+      </c>
+      <c r="J30" t="s">
         <v>326</v>
       </c>
-      <c r="J30" t="s">
-        <v>328</v>
-      </c>
       <c r="K30" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L30" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" ht="25.5" customHeight="1" spans="1:13">
@@ -8584,13 +8601,13 @@
         <v>46211</v>
       </c>
       <c r="B31" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C31" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E31" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F31">
         <v>33</v>
@@ -8599,22 +8616,22 @@
         <v>17821355492</v>
       </c>
       <c r="H31" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I31" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J31" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="K31" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M31" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
